--- a/TP3/tabla_diferencia_medias.xlsx
+++ b/TP3/tabla_diferencia_medias.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,11 @@
           <t>p_valor</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>significativa_5pct</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -469,6 +474,9 @@
       <c r="F2" t="n">
         <v>0</v>
       </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -491,6 +499,9 @@
       <c r="F3" t="n">
         <v>0.3308</v>
       </c>
+      <c r="G3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -513,6 +524,9 @@
       <c r="F4" t="n">
         <v>0.7737000000000001</v>
       </c>
+      <c r="G4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -535,6 +549,9 @@
       <c r="F5" t="n">
         <v>0.0044</v>
       </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -557,6 +574,9 @@
       <c r="F6" t="n">
         <v>0.8501</v>
       </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -565,19 +585,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.0189</v>
+        <v>13.292</v>
       </c>
       <c r="C7" t="n">
         <v>13.4263</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4074</v>
+        <v>0.1343</v>
       </c>
       <c r="E7" t="n">
-        <v>40.9227</v>
+        <v>13.4937</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -587,19 +610,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13.1864</v>
+        <v>13.4595</v>
       </c>
       <c r="C8" t="n">
         <v>13.5819</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3955</v>
+        <v>0.1224</v>
       </c>
       <c r="E8" t="n">
-        <v>43.3926</v>
+        <v>13.43</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -623,6 +649,9 @@
       <c r="F9" t="n">
         <v>0.0095</v>
       </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -645,6 +674,9 @@
       <c r="F10" t="n">
         <v>0</v>
       </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -667,6 +699,9 @@
       <c r="F11" t="n">
         <v>0.0814</v>
       </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -689,6 +724,9 @@
       <c r="F12" t="n">
         <v>0.2429</v>
       </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -711,6 +749,9 @@
       <c r="F13" t="n">
         <v>0.0004</v>
       </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -733,6 +774,9 @@
       <c r="F14" t="n">
         <v>0.9376</v>
       </c>
+      <c r="G14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -755,6 +799,9 @@
       <c r="F15" t="n">
         <v>0.6743</v>
       </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -777,6 +824,9 @@
       <c r="F16" t="n">
         <v>0.928</v>
       </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -799,6 +849,9 @@
       <c r="F17" t="n">
         <v>0.4362</v>
       </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -821,6 +874,9 @@
       <c r="F18" t="n">
         <v>0.8761</v>
       </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -843,6 +899,9 @@
       <c r="F19" t="n">
         <v>0.0072</v>
       </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -865,6 +924,9 @@
       <c r="F20" t="n">
         <v>0.0325</v>
       </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -887,6 +949,9 @@
       <c r="F21" t="n">
         <v>0.7347</v>
       </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -909,6 +974,9 @@
       <c r="F22" t="n">
         <v>0.1663</v>
       </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -931,6 +999,9 @@
       <c r="F23" t="n">
         <v>0.7265</v>
       </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -953,6 +1024,9 @@
       <c r="F24" t="n">
         <v>0.2296</v>
       </c>
+      <c r="G24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -975,6 +1049,9 @@
       <c r="F25" t="n">
         <v>0.4492</v>
       </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -997,6 +1074,9 @@
       <c r="F26" t="n">
         <v>0.536</v>
       </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1019,6 +1099,9 @@
       <c r="F27" t="n">
         <v>0.1992</v>
       </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1041,6 +1124,9 @@
       <c r="F28" t="n">
         <v>0.09619999999999999</v>
       </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1063,6 +1149,9 @@
       <c r="F29" t="n">
         <v>0.2512</v>
       </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1085,6 +1174,9 @@
       <c r="F30" t="n">
         <v>0.2482</v>
       </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1107,6 +1199,9 @@
       <c r="F31" t="n">
         <v>0.0017</v>
       </c>
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1129,6 +1224,9 @@
       <c r="F32" t="n">
         <v>0.1053</v>
       </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1151,6 +1249,9 @@
       <c r="F33" t="n">
         <v>0.5239</v>
       </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1173,6 +1274,9 @@
       <c r="F34" t="n">
         <v>0.3906</v>
       </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1195,6 +1299,9 @@
       <c r="F35" t="n">
         <v>0.922</v>
       </c>
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1217,6 +1324,9 @@
       <c r="F36" t="n">
         <v>0.9319</v>
       </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1239,6 +1349,9 @@
       <c r="F37" t="n">
         <v>0.2791</v>
       </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1261,6 +1374,9 @@
       <c r="F38" t="n">
         <v>0.2969</v>
       </c>
+      <c r="G38" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1283,6 +1399,9 @@
       <c r="F39" t="n">
         <v>0.0172</v>
       </c>
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1305,6 +1424,9 @@
       <c r="F40" t="n">
         <v>0.2704</v>
       </c>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1327,6 +1449,9 @@
       <c r="F41" t="n">
         <v>0.0341</v>
       </c>
+      <c r="G41" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1349,6 +1474,9 @@
       <c r="F42" t="n">
         <v>0.6115</v>
       </c>
+      <c r="G42" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1371,6 +1499,9 @@
       <c r="F43" t="n">
         <v>0.3215</v>
       </c>
+      <c r="G43" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1393,6 +1524,9 @@
       <c r="F44" t="n">
         <v>0.8192</v>
       </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1415,6 +1549,9 @@
       <c r="F45" t="n">
         <v>0.0329</v>
       </c>
+      <c r="G45" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1437,6 +1574,9 @@
       <c r="F46" t="n">
         <v>0.0215</v>
       </c>
+      <c r="G46" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1459,6 +1599,9 @@
       <c r="F47" t="n">
         <v>0.4916</v>
       </c>
+      <c r="G47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1481,6 +1624,9 @@
       <c r="F48" t="n">
         <v>0.1531</v>
       </c>
+      <c r="G48" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1503,6 +1649,9 @@
       <c r="F49" t="n">
         <v>0.7645</v>
       </c>
+      <c r="G49" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1525,6 +1674,9 @@
       <c r="F50" t="n">
         <v>0.6785</v>
       </c>
+      <c r="G50" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1547,6 +1699,9 @@
       <c r="F51" t="n">
         <v>0.2513</v>
       </c>
+      <c r="G51" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1569,6 +1724,9 @@
       <c r="F52" t="n">
         <v>0.1185</v>
       </c>
+      <c r="G52" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1591,6 +1749,9 @@
       <c r="F53" t="n">
         <v>0.1435</v>
       </c>
+      <c r="G53" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1613,6 +1774,9 @@
       <c r="F54" t="n">
         <v>0.0247</v>
       </c>
+      <c r="G54" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1635,6 +1799,9 @@
       <c r="F55" t="n">
         <v>0.1723</v>
       </c>
+      <c r="G55" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1657,6 +1824,9 @@
       <c r="F56" t="n">
         <v>0.0005999999999999999</v>
       </c>
+      <c r="G56" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1679,203 +1849,8 @@
       <c r="F57" t="n">
         <v>0.0128</v>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>cat_ocup_cat_Obrero o empleado</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0.7236</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0.7078</v>
-      </c>
-      <c r="D58" t="n">
-        <v>-0.0158</v>
-      </c>
-      <c r="E58" t="n">
-        <v>-3.537</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.0004</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>cat_ocup_cat_Patron</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>0.0358</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.0366</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0.4216</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0.6733</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>cat_ocup_cat_Trab. familiar sin remuneracion</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>0.0044</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.0046</v>
-      </c>
-      <c r="D60" t="n">
-        <v>0.0001</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.8556</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>comprobante_sal_cat_Factura</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>0.0291</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0.0295</v>
-      </c>
-      <c r="D61" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0.2937</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.769</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>comprobante_sal_cat_Nada</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>0.2083</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0.2088</v>
-      </c>
-      <c r="D62" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0.1343</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.8931</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>comprobante_sal_cat_Recibo_nosello</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0.0152</v>
-      </c>
-      <c r="D63" t="n">
-        <v>-0.0019</v>
-      </c>
-      <c r="E63" t="n">
-        <v>-1.4906</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0.1361</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>comprobante_sal_cat_Recibo_sello</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>0.4639</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0.4495</v>
-      </c>
-      <c r="D64" t="n">
-        <v>-0.0145</v>
-      </c>
-      <c r="E64" t="n">
-        <v>-2.9301</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.0034</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>alcance_recibo_cat_Totalidad</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>0.4456</v>
-      </c>
-      <c r="C65" t="n">
-        <v>0.4319</v>
-      </c>
-      <c r="D65" t="n">
-        <v>-0.0137</v>
-      </c>
-      <c r="E65" t="n">
-        <v>-2.7794</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0.0054</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>parte_sueldo_cat_Totalidad</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>0.0055</v>
-      </c>
-      <c r="C66" t="n">
-        <v>0.0057</v>
-      </c>
-      <c r="D66" t="n">
-        <v>0.0002</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0.2696</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0.7874</v>
+      <c r="G57" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
